--- a/artfynd/A 20108-2026 artfynd.xlsx
+++ b/artfynd/A 20108-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132846373</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20108-2026 artfynd.xlsx
+++ b/artfynd/A 20108-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133150716</v>
       </c>
       <c r="B3" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20108-2026 artfynd.xlsx
+++ b/artfynd/A 20108-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132846373</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,59 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133150716</v>
+        <v>132831976</v>
       </c>
       <c r="B3" t="n">
-        <v>58126</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgubbens mosse, Lillgubbens mosse, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476704</v>
+        <v>476670</v>
       </c>
       <c r="R3" t="n">
-        <v>6571985</v>
+        <v>6572025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spel/sång.</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +886,367 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132846170</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillgubbens mosse, Lillgubbens mosse, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>476659</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6572046</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132844172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillgubbens mosse, Lillgubbens mosse, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476660</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6572029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spel/sång</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133150716</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillgubbens mosse, Lillgubbens mosse, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476704</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571985</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20108-2026 artfynd.xlsx
+++ b/artfynd/A 20108-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132831976</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132846170</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844172</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133150716</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>